--- a/testplan/testplan_uvm11d.xlsx
+++ b/testplan/testplan_uvm11d.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HCMUS\UVM\testplan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78C9711F-3A6E-484E-9ACF-127E070E2AD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC5D2EB-FCF8-4B80-A0CD-3E054D34A37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TESTCASES" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="345">
   <si>
     <t>HPDcache UVM 1.1d Testplan  —  cv32a6_imac_sv32 + Domino Prefetcher  |  QuestaSim 23.3 Starter Edition</t>
   </si>
@@ -386,62 +386,7 @@
 covers sustained path</t>
   </si>
   <si>
-    <t>OUT OF SCOPE
-(this TB)</t>
-  </si>
-  <si>
-    <t>1.1–1.3</t>
-  </si>
-  <si>
-    <t>Core RISC-V
-ALU/Branch/CSR</t>
-  </si>
-  <si>
     <t>—</t>
-  </si>
-  <si>
-    <t>Requires full CVA6 pipeline + ISA agent. Not instantiated in this TB.</t>
-  </si>
-  <si>
-    <t>High/Med</t>
-  </si>
-  <si>
-    <t>OUT OF SCOPE
-No core pipeline
-agent in testbench</t>
-  </si>
-  <si>
-    <t>2.1–2.3</t>
-  </si>
-  <si>
-    <t>ICache Fetch /
-FENCE.I</t>
-  </si>
-  <si>
-    <t>Requires ICache model + icache_if. Not instantiated in this TB.</t>
-  </si>
-  <si>
-    <t>High/Critical</t>
-  </si>
-  <si>
-    <t>OUT OF SCOPE
-No icache_if
-agent in testbench</t>
-  </si>
-  <si>
-    <t>PERF</t>
-  </si>
-  <si>
-    <t>All Performance
-Tests (PT1–PT5)</t>
-  </si>
-  <si>
-    <t>CPI/AMAT/IPC metrics require pipeline instrumentation. Starter Edition lacks profiling.</t>
-  </si>
-  <si>
-    <t>OUT OF SCOPE
-No perf counters
-in Starter Edition</t>
   </si>
   <si>
     <t>Coverage Plan  —  UVM 1.1d compatible  (manual counters replace covergroup/cross)</t>
@@ -1137,12 +1082,156 @@
   <si>
     <t>Test Name</t>
   </si>
+  <si>
+    <t>FULL CORE TEST</t>
+  </si>
+  <si>
+    <t>Core RISC V CV32A6_IMAC</t>
+  </si>
+  <si>
+    <t>ALU &amp; Pipeline</t>
+  </si>
+  <si>
+    <t>core_basic_alu_ops</t>
+  </si>
+  <si>
+    <t>Verify decode, execute and write-back of integer ALU instructions using a bare-metal RISC-V program.</t>
+  </si>
+  <si>
+    <t>Load ALU program -&gt; Release reset -&gt; CPU executes ADD/SUB/AND/OR/XOR/SLT -&gt; Monitor commit and register write-back -&gt; Scoreboard compares GPR values.</t>
+  </si>
+  <si>
+    <t>All committed register values match reference model; no illegal commit; UVM_ERROR=0.</t>
+  </si>
+  <si>
+    <t>Branch &amp; Jump</t>
+  </si>
+  <si>
+    <t>core_branch_prediction_flush</t>
+  </si>
+  <si>
+    <t>Verify branch/jump execution, PC redirection and pipeline flush.</t>
+  </si>
+  <si>
+    <t>Load branch program -&gt; Execute BEQ/BNE/JAL/JALR -&gt; Monitor PC trace and commit sequence -&gt; Compare expected control flow.</t>
+  </si>
+  <si>
+    <t>Correct PC redirection, wrong-path instructions never commit, UVM_ERROR=0.</t>
+  </si>
+  <si>
+    <t>CSR &amp; Exception</t>
+  </si>
+  <si>
+    <t>core_exception_trap</t>
+  </si>
+  <si>
+    <t>Verify CSR access and synchronous exception handling (ECALL/illegal instruction).</t>
+  </si>
+  <si>
+    <t>Load CSR/ECALL program -&gt; Execute CSR instructions and exception -&gt; Monitor CSR updates, mepc and mcause -&gt; Compare with expected results.</t>
+  </si>
+  <si>
+    <t>CSR values, mepc and mcause are correct; execution resumes at correct handler; UVM_ERROR=0.</t>
+  </si>
+  <si>
+    <t>INSTRUCTION L1 CACHE</t>
+  </si>
+  <si>
+    <t>Sequential Fetch</t>
+  </si>
+  <si>
+    <t>icache_seq_fetch_hit_miss</t>
+  </si>
+  <si>
+    <t>Verify sequential instruction fetch, cache refill and cache hits.</t>
+  </si>
+  <si>
+    <t>Execute linear instruction stream -&gt; Observe ICache requests and AXI refill -&gt; Continue execution after refill.</t>
+  </si>
+  <si>
+    <t>First access causes refill; subsequent accesses hit in ICache; instructions execute correctly.</t>
+  </si>
+  <si>
+    <t>Branch Fetch</t>
+  </si>
+  <si>
+    <t>icache_jump_target_miss</t>
+  </si>
+  <si>
+    <t>Verify instruction fetch redirection after branch/jump.</t>
+  </si>
+  <si>
+    <t>Execute branch-intensive program -&gt; Observe fetch cancellation and new fetch request after redirect.</t>
+  </si>
+  <si>
+    <t>Old fetch is discarded, new fetch follows redirected PC, correct instruction sequence commits.</t>
+  </si>
+  <si>
+    <t>Cache Coherency</t>
+  </si>
+  <si>
+    <t>icache_fence_i_flush</t>
+  </si>
+  <si>
+    <t>Verify ICache invalidation after FENCE.I.</t>
+  </si>
+  <si>
+    <t>Modify instruction memory -&gt; Execute FENCE.I -&gt; Re-fetch modified code -&gt; Monitor committed instructions.</t>
+  </si>
+  <si>
+    <t>CPU executes updated instruction after FENCE.I; stale instructions are never executed; UVM_ERROR=0.</t>
+  </si>
+  <si>
+    <t>HIGH PERFORMANCE DATA CACHE</t>
+  </si>
+  <si>
+    <t>PREFETCHER DATA CACHE</t>
+  </si>
+  <si>
+    <t>STRESS / RANDOM TEST</t>
+  </si>
+  <si>
+    <t>REQUIRES NEW AGENTS
+isa_agent: commit_monitor + isa_driver
+Reference: Spike ISS or hardcoded golden table
+run_phase only; no rand/randomize</t>
+  </si>
+  <si>
+    <t>REQUIRES NEW AGENTS
+isa_agent: commit_monitor
+PC range check replaces SVA (UVM 1.1d)
+run_phase only</t>
+  </si>
+  <si>
+    <t>REQUIRES NEW AGENTS
+isa_agent: commit_monitor + csr_monitor
+Priority upgraded to High (exception path critical)
+run_phase only; expected values hardcoded from .hex</t>
+  </si>
+  <si>
+    <t>REQUIRES NEW AGENTS
+icache_agent: fetch_monitor
+Level 1 independent; Level 2 depends on TC 1.x
+run_phase only</t>
+  </si>
+  <si>
+    <t>REQUIRES NEW AGENTS
+icache_agent: fetch_monitor
+Signal name fetch_kill_i — verify in CVA6 RTL
+run_phase only</t>
+  </si>
+  <si>
+    <t>REQUIRES NEW AGENTS
+icache_agent + isa_agent (TC 1.x dependency)
+Instruction memory modified via data AXI store path
+run_phase only</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1184,6 +1273,19 @@
       <sz val="10"/>
       <color rgb="FF7F7F7F"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1234,7 +1336,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1257,27 +1359,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1338,6 +1442,43 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1641,499 +1782,595 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="32" customWidth="1"/>
-    <col min="5" max="5" width="36" customWidth="1"/>
-    <col min="6" max="6" width="42" customWidth="1"/>
-    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="5" max="5" width="35.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="57.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="56.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="9" max="9" width="41.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
     </row>
     <row r="2" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+    </row>
+    <row r="4" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="23"/>
+      <c r="B5" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="23"/>
+      <c r="B6" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+    </row>
+    <row r="8" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="23"/>
+      <c r="B9" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="23"/>
+      <c r="B10" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="23"/>
+      <c r="B11" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="B12" s="25"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+    </row>
+    <row r="13" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="23"/>
+      <c r="B14" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="23"/>
+      <c r="B15" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="23"/>
+      <c r="B16" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="28" t="s">
+        <v>303</v>
+      </c>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+    </row>
+    <row r="18" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="B18" s="22">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>306</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>308</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="H18" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="33" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="23"/>
+      <c r="B19" s="22">
+        <v>1.2</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>311</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>312</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>313</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>314</v>
+      </c>
+      <c r="H19" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="33" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="23"/>
+      <c r="B20" s="22">
+        <v>1.3</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>316</v>
+      </c>
+      <c r="E20" s="22" t="s">
         <v>317</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-    </row>
-    <row r="4" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" s="9" t="s">
+      <c r="F20" s="22" t="s">
+        <v>318</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="H20" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="33" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="B21" s="22">
+        <v>2.1</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>322</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>323</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>324</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>325</v>
+      </c>
+      <c r="H21" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="13" t="s">
+      <c r="I21" s="34" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="23"/>
+      <c r="B22" s="22">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>326</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>327</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>328</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>329</v>
+      </c>
+      <c r="G22" s="22" t="s">
+        <v>330</v>
+      </c>
+      <c r="H22" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="34" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="23"/>
+      <c r="B23" s="22">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>331</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>332</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>333</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="G23" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="H23" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-    </row>
-    <row r="8" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="H10" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-    </row>
-    <row r="13" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="G13" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="I13" s="18" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" s="10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="G15" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="H15" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="I16" s="18" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-    </row>
-    <row r="18" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="I18" s="19" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="I19" s="19" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="I20" s="19" t="s">
-        <v>107</v>
+      <c r="I23" s="34" t="s">
+        <v>344</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A7:I7"/>
+  <mergeCells count="10">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A17:I17"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A12:I12"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="A7:I7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2153,313 +2390,313 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+    </row>
+    <row r="2" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+    </row>
+    <row r="4" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="D5" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="E5" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="F5" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="5" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="C6" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-    </row>
-    <row r="4" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="D6" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="E6" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="F6" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D4" s="8" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+    </row>
+    <row r="8" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+      <c r="C8" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="D8" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="E8" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="F8" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="E5" s="12" t="s">
+    </row>
+    <row r="9" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="B9" s="3" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="C9" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="D9" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="E9" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="F9" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="E6" s="8" t="s">
+    </row>
+    <row r="10" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="C10" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="D10" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="E10" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="F10" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="D8" s="12" t="s">
+    </row>
+    <row r="11" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+    </row>
+    <row r="12" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="C12" s="3" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+      <c r="D12" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="E12" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="F12" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D9" s="8" t="s">
+    </row>
+    <row r="13" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="B13" s="25"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+    </row>
+    <row r="14" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="C14" s="7" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="D14" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="E14" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="F14" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="D10" s="12" t="s">
+    </row>
+    <row r="15" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="C15" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="D15" s="3" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="E15" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="8" t="s">
+      <c r="F15" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C12" s="8" t="s">
+    </row>
+    <row r="16" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+    </row>
+    <row r="17" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="C17" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="E17" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="12" t="s">
+      <c r="F17" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C14" s="12" t="s">
+    </row>
+    <row r="18" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="29" t="s">
         <v>160</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="B18" s="25"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+    </row>
+    <row r="19" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="C19" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="D19" s="15" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="8" t="s">
+      <c r="E19" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="F19" s="15" t="s">
         <v>164</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-    </row>
-    <row r="17" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-    </row>
-    <row r="19" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="F19" s="20" t="s">
-        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -2490,133 +2727,133 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="26" t="s">
+        <v>165</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+    </row>
+    <row r="2" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="E4" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="5" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="B5" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="E5" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="F5" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C3" s="8" t="s">
+    </row>
+    <row r="6" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="B6" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="C6" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="D6" s="15" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="E6" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="F6" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="C4" s="12" t="s">
+    </row>
+    <row r="7" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="B7" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="E4" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="F4" s="12" t="s">
+      <c r="C7" s="7" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="E7" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>198</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>205</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>210</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>211</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -2641,243 +2878,243 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+    </row>
+    <row r="2" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16"/>
+      <c r="B3" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="17"/>
+    </row>
+    <row r="4" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="16"/>
+      <c r="B6" s="17" t="s">
         <v>214</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+    </row>
+    <row r="7" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="21"/>
-      <c r="B3" s="22" t="s">
+      <c r="E7" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="22"/>
-    </row>
-    <row r="4" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="F7" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C8" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E8" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="F4" s="18" t="s">
+      <c r="F8" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="B5" s="11" t="s">
+      <c r="C9" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="D9" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="E9" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="F9" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="B10" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="19"/>
+    </row>
+    <row r="11" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="21"/>
-      <c r="B6" s="22" t="s">
+      <c r="B11" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="22"/>
-    </row>
-    <row r="7" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="B7" s="7" t="s">
+      <c r="C11" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D11" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="E11" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="F11" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="B8" s="11" t="s">
+    </row>
+    <row r="12" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="B12" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="C12" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="D12" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="B9" s="7" t="s">
+      <c r="E12" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="F12" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="B13" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="C13" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="F9" s="10" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="23"/>
-      <c r="B10" s="24" t="s">
+      <c r="D13" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="24"/>
-    </row>
-    <row r="11" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="20" t="s">
+      <c r="E13" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="F13" s="14" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="B14" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="C14" s="15" t="s">
         <v>246</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="D14" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="E14" s="15" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>250</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>253</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="20" t="s">
-        <v>254</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>256</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>257</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>258</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="20" t="s">
-        <v>259</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="C14" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>248</v>
+      <c r="F14" s="14" t="s">
+        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -2901,216 +3138,216 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+    </row>
+    <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
         <v>264</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-    </row>
-    <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="B5" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="D5" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="E5" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="D2" s="5" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="20" t="s">
         <v>268</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="B6" s="13" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="20" t="s">
+      <c r="C6" s="20" t="s">
         <v>270</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="D6" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="E6" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="D3" s="20" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="B7" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+      <c r="D7" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="E7" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="C4" s="20" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="20" t="s">
         <v>277</v>
       </c>
-      <c r="D4" s="20" t="s">
+      <c r="B8" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="E4" s="20" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+      <c r="C8" s="20" t="s">
         <v>279</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>276</v>
-      </c>
-      <c r="C5" s="20" t="s">
+      <c r="D8" s="20" t="s">
         <v>280</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="E8" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="E5" s="20" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="20" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="B9" s="13" t="s">
         <v>283</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="C9" s="20" t="s">
         <v>284</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="D9" s="20" t="s">
         <v>285</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="E9" s="20" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="B10" s="13" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="20" t="s">
+      <c r="C10" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>276</v>
-      </c>
-      <c r="C7" s="20" t="s">
+      <c r="D10" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="E10" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="E7" s="20" t="s">
+    </row>
+    <row r="11" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="21" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25" t="s">
+      <c r="B11" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="C11" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="D11" s="21" t="s">
         <v>294</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="E11" s="21" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="B12" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="C12" s="21" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="25" t="s">
+      <c r="D12" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="E12" s="21" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="21" t="s">
         <v>298</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="B13" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="C13" s="21" t="s">
         <v>299</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D13" s="21" t="s">
         <v>300</v>
       </c>
-      <c r="E9" s="25" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="25" t="s">
+      <c r="E13" s="21" t="s">
         <v>301</v>
-      </c>
-      <c r="B10" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>303</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>304</v>
-      </c>
-      <c r="E10" s="25" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="26" t="s">
-        <v>306</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="C11" s="26" t="s">
-        <v>308</v>
-      </c>
-      <c r="D11" s="26" t="s">
-        <v>309</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="26" t="s">
-        <v>310</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="D12" s="26" t="s">
-        <v>312</v>
-      </c>
-      <c r="E12" s="26" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26" t="s">
-        <v>313</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>307</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>314</v>
-      </c>
-      <c r="D13" s="26" t="s">
-        <v>315</v>
-      </c>
-      <c r="E13" s="26" t="s">
-        <v>316</v>
       </c>
     </row>
   </sheetData>

--- a/testplan/testplan_uvm11d.xlsx
+++ b/testplan/testplan_uvm11d.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HCMUS\UVM\testplan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC5D2EB-FCF8-4B80-A0CD-3E054D34A37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CB82E77-31AE-4AB9-B650-7AD610D82C79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TESTCASES" sheetId="1" r:id="rId1"/>
@@ -1231,7 +1231,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1258,24 +1258,6 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color rgb="FFC55A11"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -1284,6 +1266,40 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFC55A11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1378,7 +1394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1389,9 +1405,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1401,21 +1414,6 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1443,43 +1441,72 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1783,594 +1810,595 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="32" customWidth="1"/>
-    <col min="5" max="5" width="35.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="57.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="56.77734375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" customWidth="1"/>
-    <col min="9" max="9" width="41.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22" style="39" customWidth="1"/>
+    <col min="2" max="2" width="8" style="39" customWidth="1"/>
+    <col min="3" max="3" width="20" style="39" customWidth="1"/>
+    <col min="4" max="4" width="32" style="39" customWidth="1"/>
+    <col min="5" max="5" width="35.88671875" style="39" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="57.5546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="56.77734375" style="39" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" style="39" customWidth="1"/>
+    <col min="9" max="9" width="41.5546875" style="39" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="39"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-    </row>
-    <row r="2" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+    </row>
+    <row r="2" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="25" t="s">
         <v>302</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="25" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="24" t="s">
+    <row r="3" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-    </row>
-    <row r="4" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
+      <c r="B3" s="27"/>
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+    </row>
+    <row r="4" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
         <v>336</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="29" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="23"/>
-      <c r="B5" s="22" t="s">
+    <row r="5" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="21"/>
+      <c r="B5" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="29" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23"/>
-      <c r="B6" s="22" t="s">
+    <row r="6" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="21"/>
+      <c r="B6" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="29" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24" t="s">
+    <row r="7" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-    </row>
-    <row r="8" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="23" t="s">
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+    </row>
+    <row r="8" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
         <v>337</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="22" t="s">
+      <c r="G8" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="29" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="23"/>
-      <c r="B9" s="22" t="s">
+    <row r="9" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="21"/>
+      <c r="B9" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="22" t="s">
+      <c r="G9" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="29" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="23"/>
-      <c r="B10" s="22" t="s">
+    <row r="10" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="21"/>
+      <c r="B10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="29" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="23"/>
-      <c r="B11" s="22" t="s">
+    <row r="11" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="21"/>
+      <c r="B11" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="29" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="24" t="s">
+    <row r="12" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25"/>
-    </row>
-    <row r="13" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="23" t="s">
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+    </row>
+    <row r="13" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
         <v>338</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="I13" s="35" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="23"/>
-      <c r="B14" s="22" t="s">
+    <row r="14" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="21"/>
+      <c r="B14" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="29" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="23"/>
-      <c r="B15" s="22" t="s">
+    <row r="15" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="21"/>
+      <c r="B15" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="G15" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="H15" s="12" t="s">
+      <c r="H15" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="29" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="23"/>
-      <c r="B16" s="22" t="s">
+    <row r="16" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="21"/>
+      <c r="B16" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="13" t="s">
+      <c r="I16" s="35" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="28" t="s">
+    <row r="17" spans="1:9" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="36" t="s">
         <v>303</v>
       </c>
-      <c r="B17" s="25"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-    </row>
-    <row r="18" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="23" t="s">
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+    </row>
+    <row r="18" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
         <v>304</v>
       </c>
-      <c r="B18" s="22">
+      <c r="B18" s="16">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="16" t="s">
         <v>305</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="16" t="s">
         <v>306</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="16" t="s">
         <v>307</v>
       </c>
-      <c r="F18" s="22" t="s">
+      <c r="F18" s="16" t="s">
         <v>308</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="H18" s="30" t="s">
+      <c r="H18" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="I18" s="33" t="s">
+      <c r="I18" s="37" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23"/>
-      <c r="B19" s="22">
+    <row r="19" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="21"/>
+      <c r="B19" s="16">
         <v>1.2</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="16" t="s">
         <v>310</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="D19" s="16" t="s">
         <v>311</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="16" t="s">
         <v>312</v>
       </c>
-      <c r="F19" s="22" t="s">
+      <c r="F19" s="16" t="s">
         <v>313</v>
       </c>
-      <c r="G19" s="22" t="s">
+      <c r="G19" s="16" t="s">
         <v>314</v>
       </c>
-      <c r="H19" s="30" t="s">
+      <c r="H19" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="I19" s="33" t="s">
+      <c r="I19" s="37" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="23"/>
-      <c r="B20" s="22">
+    <row r="20" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="21"/>
+      <c r="B20" s="16">
         <v>1.3</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="16" t="s">
         <v>315</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="16" t="s">
         <v>316</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="16" t="s">
         <v>317</v>
       </c>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="16" t="s">
         <v>318</v>
       </c>
-      <c r="G20" s="22" t="s">
+      <c r="G20" s="16" t="s">
         <v>319</v>
       </c>
-      <c r="H20" s="31" t="s">
+      <c r="H20" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="I20" s="33" t="s">
+      <c r="I20" s="37" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="23" t="s">
+    <row r="21" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="21" t="s">
         <v>320</v>
       </c>
-      <c r="B21" s="22">
+      <c r="B21" s="16">
         <v>2.1</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="16" t="s">
         <v>321</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="16" t="s">
         <v>322</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="E21" s="16" t="s">
         <v>323</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="F21" s="16" t="s">
         <v>324</v>
       </c>
-      <c r="G21" s="22" t="s">
+      <c r="G21" s="16" t="s">
         <v>325</v>
       </c>
-      <c r="H21" s="30" t="s">
+      <c r="H21" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="I21" s="34" t="s">
+      <c r="I21" s="38" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="23"/>
-      <c r="B22" s="22">
+    <row r="22" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="21"/>
+      <c r="B22" s="16">
         <v>2.2000000000000002</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="16" t="s">
         <v>326</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="16" t="s">
         <v>327</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="16" t="s">
         <v>328</v>
       </c>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="16" t="s">
         <v>329</v>
       </c>
-      <c r="G22" s="22" t="s">
+      <c r="G22" s="16" t="s">
         <v>330</v>
       </c>
-      <c r="H22" s="30" t="s">
+      <c r="H22" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="I22" s="34" t="s">
+      <c r="I22" s="38" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="23"/>
-      <c r="B23" s="22">
+    <row r="23" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="21"/>
+      <c r="B23" s="16">
         <v>2.2999999999999998</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="16" t="s">
         <v>331</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="16" t="s">
         <v>332</v>
       </c>
-      <c r="E23" s="22" t="s">
+      <c r="E23" s="16" t="s">
         <v>333</v>
       </c>
-      <c r="F23" s="22" t="s">
+      <c r="F23" s="16" t="s">
         <v>334</v>
       </c>
-      <c r="G23" s="22" t="s">
+      <c r="G23" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="H23" s="32" t="s">
+      <c r="H23" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="I23" s="34" t="s">
+      <c r="I23" s="38" t="s">
         <v>344</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="A7:I7"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A17:I17"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="A13:A16"/>
-    <mergeCell ref="A7:I7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2390,14 +2418,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2420,14 +2448,14 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
     </row>
     <row r="4" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
@@ -2450,22 +2478,22 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="6" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2490,32 +2518,32 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
     </row>
     <row r="8" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>124</v>
       </c>
     </row>
@@ -2540,34 +2568,34 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="24" t="s">
+      <c r="A11" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
     </row>
     <row r="12" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
@@ -2590,32 +2618,32 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="6" t="s">
         <v>148</v>
       </c>
     </row>
@@ -2640,62 +2668,62 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
     </row>
     <row r="17" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="6" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
     </row>
     <row r="19" spans="1:6" ht="67.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="9" t="s">
         <v>164</v>
       </c>
     </row>
@@ -2727,14 +2755,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2777,22 +2805,22 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>181</v>
       </c>
     </row>
@@ -2817,42 +2845,42 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="E6" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="9" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>198</v>
       </c>
     </row>
@@ -2878,14 +2906,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -2908,14 +2936,14 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16"/>
-      <c r="B3" s="17" t="s">
+      <c r="A3" s="10"/>
+      <c r="B3" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="17"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="11"/>
     </row>
     <row r="4" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -2933,39 +2961,39 @@
       <c r="E4" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="7" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="16"/>
-      <c r="B6" s="17" t="s">
+      <c r="A6" s="10"/>
+      <c r="B6" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="17"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="11"/>
     </row>
     <row r="7" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
@@ -2983,27 +3011,27 @@
       <c r="E7" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>213</v>
       </c>
     </row>
@@ -3023,97 +3051,97 @@
       <c r="E9" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="18"/>
-      <c r="B10" s="19" t="s">
+      <c r="A10" s="12"/>
+      <c r="B10" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="19"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="13"/>
     </row>
     <row r="11" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="9" t="s">
         <v>232</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="8" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="8" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="9" t="s">
         <v>239</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="9" t="s">
         <v>241</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="9" t="s">
         <v>243</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="8" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="8" t="s">
         <v>233</v>
       </c>
     </row>
@@ -3138,13 +3166,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="17" t="s">
         <v>249</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
     </row>
     <row r="2" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
@@ -3164,189 +3192,189 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="9" t="s">
         <v>255</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="9" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="9" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="9" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="14" t="s">
         <v>270</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="14" t="s">
         <v>271</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="14" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="9" t="s">
         <v>273</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="9" t="s">
         <v>274</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="9" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="14" t="s">
         <v>277</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="14" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="7" t="s">
         <v>283</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="14" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="14" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="15" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="15" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="15" t="s">
         <v>298</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="15" t="s">
         <v>301</v>
       </c>
     </row>
